--- a/converter/device_config.xlsx
+++ b/converter/device_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\code_test\VEGA_SDK\converter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7002EC2C-5498-4E6D-BC6B-1EA2ACE43D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B338024A-77A1-4792-A554-75C76B390077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17424" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="devices" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="38">
   <si>
     <t>Domain</t>
   </si>
@@ -116,6 +116,30 @@
   </si>
   <si>
     <t>Master Bedroom AC Fan Speed</t>
+  </si>
+  <si>
+    <t>electricity_high</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>electricity_low</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>switch_ch1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set_init_electricity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DK5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -499,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
@@ -716,6 +740,86 @@
         <v>31</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/converter/device_config.xlsx
+++ b/converter/device_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\code_test\VEGA_SDK\converter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eyeye\Documents\code_test\VEGA_SDK\converter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B338024A-77A1-4792-A554-75C76B390077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAB2157-CBAD-4D80-9845-6883E8929D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17424" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="devices" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="40">
   <si>
     <t>Domain</t>
   </si>
@@ -43,110 +43,371 @@
     <t>Loop_Description</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>DK1</t>
+    <t>switch_ch1</t>
+  </si>
+  <si>
+    <t>diming</t>
+  </si>
+  <si>
+    <t>switch_ch2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>00006QWA</t>
+  </si>
+  <si>
+    <t>00009LUI</t>
+  </si>
+  <si>
+    <t>0000JKF1</t>
+  </si>
+  <si>
+    <t>0000IQBA</t>
+  </si>
+  <si>
+    <t>0000ASKL</t>
+  </si>
+  <si>
+    <t>0000FTLA</t>
+  </si>
+  <si>
+    <t>0000AACB</t>
+  </si>
+  <si>
+    <t>0000788L</t>
+  </si>
+  <si>
+    <t>0000BRDB</t>
   </si>
   <si>
     <t>switch</t>
   </si>
   <si>
-    <t>switch_ch1</t>
-  </si>
-  <si>
-    <t>Living Room Light</t>
-  </si>
-  <si>
-    <t>switch_ch2</t>
-  </si>
-  <si>
-    <t>Dining Room Light</t>
+    <t>00004473</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EKLB3_調光模組LC01</t>
+  </si>
+  <si>
+    <t>EKLB3_調光模組LC02</t>
+  </si>
+  <si>
+    <t>eastsoft</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>00006ULY</t>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC03</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC04</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC05</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC06</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC07</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC08</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC09</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>調光模組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LC10</t>
+    </r>
+  </si>
+  <si>
+    <t>0000GWLZ</t>
   </si>
   <si>
     <t>switch_ch3</t>
-  </si>
-  <si>
-    <t>Hallway Light</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>switch_ch4</t>
-  </si>
-  <si>
-    <t>Entrance Light</t>
-  </si>
-  <si>
-    <t>DK4</t>
-  </si>
-  <si>
-    <t>panel</t>
-  </si>
-  <si>
-    <t>Kitchen Panel Switch</t>
-  </si>
-  <si>
-    <t>button_id</t>
-  </si>
-  <si>
-    <t>Kitchen Panel Button ID</t>
-  </si>
-  <si>
-    <t>eastsoft</t>
-  </si>
-  <si>
-    <t>0000IPX8</t>
-  </si>
-  <si>
-    <t>00008IBU</t>
-  </si>
-  <si>
-    <t>aircondition</t>
-  </si>
-  <si>
-    <t>power_on</t>
-  </si>
-  <si>
-    <t>Master Bedroom AC Power</t>
-  </si>
-  <si>
-    <t>rev_speed</t>
-  </si>
-  <si>
-    <t>Master Bedroom AC Fan Speed</t>
-  </si>
-  <si>
-    <t>electricity_high</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>electricity_low</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>meter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>switch_ch1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>set_init_electricity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DK5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>路開關執行器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ch1</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>路開關執行器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ch2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>路開關執行器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ch3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EKLB3_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>路開關執行器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ch4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -155,11 +416,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -170,7 +459,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -178,15 +467,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{30BD3E3F-D0E0-4084-88AA-3A3B7ACC3A81}"/>
+    <cellStyle name="一般 3" xfId="2" xr:uid="{52857993-04F1-4996-BD96-F9456A3FF20F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -521,26 +880,48 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="401" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C4BA63C0-FDD9-41A2-BD88-A5A868CAD90B}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;3897d5c1-1205-4966-b58e-3b98e0f83d6c&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.90625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="26.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -556,275 +937,563 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G20" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="G21" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="G22" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23">
         <v>22</v>
       </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="G23" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
         <v>34</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F24">
+        <v>23</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
         <v>35</v>
       </c>
-      <c r="F10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13">
-        <v>22</v>
+      <c r="F25">
+        <v>24</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>